--- a/DOSSIES_MULTIFORMATO/BRADESCO/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/BRADESCO/dossie.xlsx
@@ -5062,9 +5062,2126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Serviços</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Número</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Comp.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Atraso</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Corrigido</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Ações</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>143025</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>07/2023</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>61.264,00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>955 dias</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>143777</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>08/2023</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>60.814,00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>925 dias</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>144500</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>09/2023</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>60.784,00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>896 dias</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>145256</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10/2023</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>60.600,00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>864 dias</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>146017</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>11/2023</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>60.960,00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>833 dias</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>146774</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>12/2023</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60.966,00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>804 dias</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>147530</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>01/2024</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>60.884,00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>771 dias</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>148217</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>02/2024</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>59.946,00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>742 dias</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>151258</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>06/2024</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>60.716,00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>623 dias</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>086/2024</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>151259</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>06/2024</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>26.548,00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>623 dias</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>086/2024</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>152041</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>07/2024</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>26.542,00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>590 dias</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>151999</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>07/2024</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>60.654,00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>590 dias</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>152810</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>08/2024</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>60.362,00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>560 dias</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>086/2024</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>152827</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>08/2024</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>26.178,00</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>560 dias</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>153589</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>09/2024</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>59.950,00</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>531 dias</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>086/2024</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>153588</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>09/2024</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>26.084,00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>531 dias</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>154375</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>10/2024</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>59.444,00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>497 dias</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>086/2024</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>154377</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>10/2024</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>26.030,00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>497 dias</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>156825</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>01/2025</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>59.838,00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>405 dias</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>157591</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>58.828,00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>377 dias</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>086/2024</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>157590</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>25.922,00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>377 dias</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>158360</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>58.692,00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>349 dias</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>086/2024</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>158361</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>26.254,00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>349 dias</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>086/2024</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>159139</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>04/2025</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>27.046,00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>317 dias</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>159143</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>04/2025</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>59.426,00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>317 dias</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>086/2024</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>159775</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>05/2025</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>27.272,00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>293 dias</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>159907</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>05/2025</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>59.896,00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>289 dias</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>086/2024</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>160668</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>06/2025</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>27.546,00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>259 dias</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>160755</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>06/2025</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>60.302,00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>259 dias</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>086/2024</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>161389</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>07/2025</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>27.760,00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>232 dias</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>161397</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>07/2025</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>60.374,00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>232 dias</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>086/2024</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>162383</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>08/2025</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>27.916,00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>195 dias</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>162387</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>08/2025</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>60.076,00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>195 dias</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>163138</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>09/2025</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>60.050,00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>163 dias</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>086/2024</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>163169</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>09/2025</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>28.198,00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>163 dias</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>086/2024</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>163829</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>10/2025</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>28.538,00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>140 dias</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>119/2023</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>163956</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>10/2025</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>60.378,00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>134 dias</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>005/2025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>164840</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>11/2025</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>28.490,00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>104 dias</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>005/2025</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>164834</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>11/2025</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>60.488,00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>104 dias</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>005/2025</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>165567</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.076,00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>80 dias</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>005/2025</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>165564</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>28.328,00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>80 dias</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>005/2025</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>166431</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>01/2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.738,00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>41 dias</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BANCO BRADESCO</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>005/2025</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>166433</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>01/2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>28.576,00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>41 dias</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>